--- a/data/trans_bre/IP21B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 0,0</t>
+          <t>-18,45; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,0</t>
+          <t>0,0; 29,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 53,7</t>
+          <t>-36,16; 56,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 21,76</t>
+          <t>-41,06; 22,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 54,5</t>
+          <t>-51,96; 57,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 68,22</t>
+          <t>-39,19; 63,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 598,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,62; 112,73</t>
+          <t>-81,72; 108,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,8; —</t>
+          <t>-75,63; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 100,0</t>
+          <t>-24,73; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 54,58</t>
+          <t>-56,02; 46,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 61,78</t>
+          <t>-71,36; 61,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 0,0</t>
+          <t>-61,7; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 0,0</t>
+          <t>-53,45; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 9,7</t>
+          <t>-14,51; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 12,03</t>
+          <t>-16,32; 14,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 22,2</t>
+          <t>-20,79; 21,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 31,78</t>
+          <t>-30,15; 32,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 201,84</t>
+          <t>-86,28; 214,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 121,5</t>
+          <t>-73,48; 163,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 263,39</t>
+          <t>-63,61; 216,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-94,78; 337,47</t>
+          <t>-82,54; 492,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Edad-trans_bre.xlsx
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 0,0</t>
+          <t>-19,09; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,53</t>
+          <t>0,0; 31,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 56,55</t>
+          <t>-35,78; 51,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,06; 22,81</t>
+          <t>-39,91; 26,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 57,26</t>
+          <t>-51,88; 54,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 63,15</t>
+          <t>-36,57; 61,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 598,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 108,87</t>
+          <t>-80,0; 145,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 100,0</t>
+          <t>-26,89; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 46,8</t>
+          <t>-51,39; 55,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-71,36; 61,78</t>
+          <t>-71,49; 61,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 0,0</t>
+          <t>-61,73; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 0,0</t>
+          <t>-54,34; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 11,02</t>
+          <t>-15,24; 10,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 14,84</t>
+          <t>-18,34; 13,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 21,02</t>
+          <t>-20,5; 20,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 32,53</t>
+          <t>-33,12; 29,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 214,12</t>
+          <t>-84,24; 212,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 163,44</t>
+          <t>-74,33; 143,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 216,21</t>
+          <t>-63,23; 187,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 492,8</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 0,0</t>
+          <t>-21,72; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,89</t>
+          <t>0,0; 29,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,11</t>
+          <t>19,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 51,92</t>
+          <t>-35,63; 53,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 26,64</t>
+          <t>-45,27; 21,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 54,6</t>
+          <t>-51,62; 54,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 61,77</t>
+          <t>-35,47; 72,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 145,71</t>
+          <t>-85,62; 112,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,8; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,04%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 100,0</t>
+          <t>-25,05; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 55,18</t>
+          <t>-54,22; 54,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 61,78</t>
+          <t>-66,83; 72,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-43,84</t>
+          <t>-45,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 0,0</t>
+          <t>-57,41; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 0,0</t>
+          <t>-54,27; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 10,26</t>
+          <t>-15,7; 9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 13,43</t>
+          <t>-16,98; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 20,86</t>
+          <t>-20,88; 22,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 29,51</t>
+          <t>-32,09; 34,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,24; 212,71</t>
+          <t>-84,34; 201,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 143,92</t>
+          <t>-74,76; 121,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 187,57</t>
+          <t>-64,46; 263,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,59</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-4.39113733903731</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.586936751905146</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-21,72; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-21.71642170219155</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>29.00130461195675</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-9,66</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-26,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-35,63; 53,7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-45,27; 21,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-51,62; 54,5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-35,47; 72,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-85,62; 112,73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-74,8; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.927968765393497</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-9.655786823986217</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.378997665255104</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>19.27856502007671</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1351967922444462</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2624780784668993</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1584247544902693</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.9719755729614604</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>46,76</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>346,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-11,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-35.63084886705298</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-45.26845851544397</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-51.623974688187</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-35.46942935941289</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.8562263447017936</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7480289575528418</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-25,05; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-54,22; 54,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-66,83; 72,14</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>53.69792927722953</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21.76334081724879</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>54.49539433514536</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>72.61130100134785</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>1.127334892598005</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +783,253 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-22,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,04</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-45,5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>46.75891480452243</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.624040355116355</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.9769825356833683</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3.46219968834124</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="n">
+        <v>-0.1115974662400144</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.03211469715997952</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-57,41; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-54,27; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-25.04747786225337</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-54.22143409325207</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-66.83198304235908</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>54.58063207229311</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>72.13789252069245</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-22.57924837268483</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-14.04039176106019</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-45.49653184866331</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>-57.41347529054577</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-54.2745414454747</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-13,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-15,7; 9,7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-16,98; 12,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,88; 22,2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-32,09; 34,39</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-84,34; 201,84</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-74,76; 121,5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-64,46; 263,39</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 367,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.554704906982479</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.49521887869057</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.276135974439763</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1949990453929296</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.208165500821786</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1384197247504137</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.06011278302960361</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.007363632267357125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-15.69552620791438</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-16.97864242478489</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.88306294798407</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-32.08569542076016</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.8433909072628978</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7475832540303866</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.644635578440933</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.702580252170407</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.02827703860551</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>22.19962105568049</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>34.38706574460353</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.018416933832388</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.214969012487765</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.633865428977699</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>3.67537607925836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1037,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
